--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/6.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/6.xlsx
@@ -426,13 +426,13 @@
         <v>-6.578110429349512</v>
       </c>
       <c r="E2">
-        <v>-3.639387197030015</v>
+        <v>-4.779172405442591</v>
       </c>
       <c r="F2">
-        <v>-6.612976408701964</v>
+        <v>-6.387245463071696</v>
       </c>
       <c r="G2">
-        <v>-11.57276457702818</v>
+        <v>-13.54720869737768</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.664938785759721</v>
       </c>
       <c r="E3">
-        <v>-3.737383374556002</v>
+        <v>-5.279881247996694</v>
       </c>
       <c r="F3">
-        <v>-6.5130918672724</v>
+        <v>-6.25285279237631</v>
       </c>
       <c r="G3">
-        <v>-11.39748443290593</v>
+        <v>-13.30572591883385</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-8.899607284952912</v>
       </c>
       <c r="E4">
-        <v>-6.201797043426241</v>
+        <v>-4.982233708420537</v>
       </c>
       <c r="F4">
-        <v>-6.752524423928673</v>
+        <v>-5.950256807072873</v>
       </c>
       <c r="G4">
-        <v>-11.61998288805481</v>
+        <v>-13.54762417084286</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.06837411339539</v>
       </c>
       <c r="E5">
-        <v>-5.102867727510867</v>
+        <v>-6.367425980256784</v>
       </c>
       <c r="F5">
-        <v>-6.294893266435787</v>
+        <v>-5.831224553127598</v>
       </c>
       <c r="G5">
-        <v>-11.04910910471735</v>
+        <v>-13.03747241378671</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-11.14897408593079</v>
       </c>
       <c r="E6">
-        <v>-6.760982070841392</v>
+        <v>-7.818638874650857</v>
       </c>
       <c r="F6">
-        <v>-6.791273794296829</v>
+        <v>-5.87537902079902</v>
       </c>
       <c r="G6">
-        <v>-11.47538487999052</v>
+        <v>-13.51465113727172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.05877246917635</v>
       </c>
       <c r="E7">
-        <v>-6.875996253688204</v>
+        <v>-8.380346262088281</v>
       </c>
       <c r="F7">
-        <v>-6.207990898942897</v>
+        <v>-5.723138346042916</v>
       </c>
       <c r="G7">
-        <v>-10.28528679571454</v>
+        <v>-12.96857996111448</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.74385046195893</v>
       </c>
       <c r="E8">
-        <v>-7.619250164093132</v>
+        <v>-8.589521004976582</v>
       </c>
       <c r="F8">
-        <v>-5.985330711274806</v>
+        <v>-5.675437637520109</v>
       </c>
       <c r="G8">
-        <v>-11.55098118737978</v>
+        <v>-12.82545183526963</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.12746983004976</v>
       </c>
       <c r="E9">
-        <v>-7.754683236240529</v>
+        <v>-9.267080342952237</v>
       </c>
       <c r="F9">
-        <v>-5.754909549409888</v>
+        <v>-5.154903158744538</v>
       </c>
       <c r="G9">
-        <v>-10.81673860277036</v>
+        <v>-13.63825863134426</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.15865792423111</v>
       </c>
       <c r="E10">
-        <v>-9.695320015961592</v>
+        <v>-9.934337402560441</v>
       </c>
       <c r="F10">
-        <v>-5.511421720133209</v>
+        <v>-5.33829210458071</v>
       </c>
       <c r="G10">
-        <v>-10.3310583983405</v>
+        <v>-13.05345572765031</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.79727365599947</v>
       </c>
       <c r="E11">
-        <v>-10.97383502559915</v>
+        <v>-10.99641399700139</v>
       </c>
       <c r="F11">
-        <v>-5.828296274358702</v>
+        <v>-4.95790082301076</v>
       </c>
       <c r="G11">
-        <v>-10.50458395332694</v>
+        <v>-12.67603036235462</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.04003207372434</v>
       </c>
       <c r="E12">
-        <v>-10.11407253592488</v>
+        <v>-10.88820611058811</v>
       </c>
       <c r="F12">
-        <v>-5.632630923613042</v>
+        <v>-5.068463020262411</v>
       </c>
       <c r="G12">
-        <v>-9.627249658873605</v>
+        <v>-11.95387126896354</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.91480229489616</v>
       </c>
       <c r="E13">
-        <v>-11.82420998865552</v>
+        <v>-11.60059847063076</v>
       </c>
       <c r="F13">
-        <v>-5.70228171157523</v>
+        <v>-4.73224028860973</v>
       </c>
       <c r="G13">
-        <v>-9.399831733053372</v>
+        <v>-11.92165303977536</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.491963703009038</v>
       </c>
       <c r="E14">
-        <v>-11.97160728913118</v>
+        <v>-12.83251095425539</v>
       </c>
       <c r="F14">
-        <v>-5.293716826268666</v>
+        <v>-4.365700138381991</v>
       </c>
       <c r="G14">
-        <v>-9.245547068741176</v>
+        <v>-11.36364734694904</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.867146456008196</v>
       </c>
       <c r="E15">
-        <v>-11.6898275224779</v>
+        <v>-12.06049670542774</v>
       </c>
       <c r="F15">
-        <v>-5.145533495051474</v>
+        <v>-4.599927648462773</v>
       </c>
       <c r="G15">
-        <v>-9.491934420501435</v>
+        <v>-11.24016730887976</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.151452041869431</v>
       </c>
       <c r="E16">
-        <v>-13.22141177356011</v>
+        <v>-13.73340104486732</v>
       </c>
       <c r="F16">
-        <v>-4.811406532927876</v>
+        <v>-4.496155578811871</v>
       </c>
       <c r="G16">
-        <v>-8.271094610347781</v>
+        <v>-11.11731958500849</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.45536887952144</v>
       </c>
       <c r="E17">
-        <v>-12.74007574281082</v>
+        <v>-14.42822292576021</v>
       </c>
       <c r="F17">
-        <v>-4.70719542855349</v>
+        <v>-4.00172792710293</v>
       </c>
       <c r="G17">
-        <v>-7.705544184237467</v>
+        <v>-10.19451494757326</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.883918175057422</v>
       </c>
       <c r="E18">
-        <v>-14.21823758602454</v>
+        <v>-15.02946841975861</v>
       </c>
       <c r="F18">
-        <v>-4.325950928558656</v>
+        <v>-3.757190556326905</v>
       </c>
       <c r="G18">
-        <v>-7.921616870494619</v>
+        <v>-10.15979394595739</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.523564626203454</v>
       </c>
       <c r="E19">
-        <v>-15.29024965243832</v>
+        <v>-16.03882451980226</v>
       </c>
       <c r="F19">
-        <v>-4.239547238242252</v>
+        <v>-3.255822014149907</v>
       </c>
       <c r="G19">
-        <v>-6.948190681218398</v>
+        <v>-9.907553549683698</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.4356613028704376</v>
       </c>
       <c r="E20">
-        <v>-16.73034514314356</v>
+        <v>-16.66284823805923</v>
       </c>
       <c r="F20">
-        <v>-3.794655957220721</v>
+        <v>-3.538359082794554</v>
       </c>
       <c r="G20">
-        <v>-7.263255300190837</v>
+        <v>-10.09627119814985</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.349615054067978</v>
       </c>
       <c r="E21">
-        <v>-16.17756337797526</v>
+        <v>-18.26287131681936</v>
       </c>
       <c r="F21">
-        <v>-3.926970254102483</v>
+        <v>-2.966448429329956</v>
       </c>
       <c r="G21">
-        <v>-6.947568298657015</v>
+        <v>-9.936269221691335</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.8280046150630871</v>
       </c>
       <c r="E22">
-        <v>-17.50695126461498</v>
+        <v>-18.21874133761462</v>
       </c>
       <c r="F22">
-        <v>-3.713122238865374</v>
+        <v>-2.943753647595458</v>
       </c>
       <c r="G22">
-        <v>-7.154007297394887</v>
+        <v>-9.388910243319316</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.015868189732793</v>
       </c>
       <c r="E23">
-        <v>-17.07548731811217</v>
+        <v>-18.83321450418941</v>
       </c>
       <c r="F23">
-        <v>-3.670173874132428</v>
+        <v>-2.883311820050192</v>
       </c>
       <c r="G23">
-        <v>-7.334203601642957</v>
+        <v>-8.86093450907973</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.9481105479061376</v>
       </c>
       <c r="E24">
-        <v>-17.66612259751059</v>
+        <v>-18.6717381780239</v>
       </c>
       <c r="F24">
-        <v>-2.940083151633653</v>
+        <v>-2.545436495428927</v>
       </c>
       <c r="G24">
-        <v>-7.966564147281304</v>
+        <v>-9.242342460659163</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.6719740912272242</v>
       </c>
       <c r="E25">
-        <v>-18.17985985978476</v>
+        <v>-19.0086702296166</v>
       </c>
       <c r="F25">
-        <v>-3.128993166209483</v>
+        <v>-2.96353506117431</v>
       </c>
       <c r="G25">
-        <v>-7.479791462823487</v>
+        <v>-10.12168956680038</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2385617237720863</v>
       </c>
       <c r="E26">
-        <v>-19.81830704049997</v>
+        <v>-18.58855916745102</v>
       </c>
       <c r="F26">
-        <v>-3.04538024567311</v>
+        <v>-2.476501416902757</v>
       </c>
       <c r="G26">
-        <v>-7.124689106099102</v>
+        <v>-9.389320750966185</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.3069134989268231</v>
       </c>
       <c r="E27">
-        <v>-19.39516642922325</v>
+        <v>-19.39705027441044</v>
       </c>
       <c r="F27">
-        <v>-2.778442991957983</v>
+        <v>-2.439984496685147</v>
       </c>
       <c r="G27">
-        <v>-8.470809891095394</v>
+        <v>-9.644007640393397</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.9266248521341371</v>
       </c>
       <c r="E28">
-        <v>-19.02180280423885</v>
+        <v>-19.20388821561327</v>
       </c>
       <c r="F28">
-        <v>-2.490887673587177</v>
+        <v>-2.729484821717727</v>
       </c>
       <c r="G28">
-        <v>-8.535676720391875</v>
+        <v>-9.351123676534074</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.58935107373824</v>
       </c>
       <c r="E29">
-        <v>-18.46540731681242</v>
+        <v>-18.78269937663385</v>
       </c>
       <c r="F29">
-        <v>-2.414077306162592</v>
+        <v>-2.523058150042298</v>
       </c>
       <c r="G29">
-        <v>-7.833715265335891</v>
+        <v>-9.24181277337288</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.270274588527723</v>
       </c>
       <c r="E30">
-        <v>-17.61539010320266</v>
+        <v>-19.29572566848882</v>
       </c>
       <c r="F30">
-        <v>-3.099104013581671</v>
+        <v>-2.545545839926096</v>
       </c>
       <c r="G30">
-        <v>-8.048000257001835</v>
+        <v>-10.40512854423616</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.949261159975127</v>
       </c>
       <c r="E31">
-        <v>-17.31795540190486</v>
+        <v>-19.41044550052513</v>
       </c>
       <c r="F31">
-        <v>-2.863184148896969</v>
+        <v>-2.713182551230632</v>
       </c>
       <c r="G31">
-        <v>-8.198169913208716</v>
+        <v>-9.702766513169921</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.611715277381651</v>
       </c>
       <c r="E32">
-        <v>-17.80034203862393</v>
+        <v>-18.67248537623517</v>
       </c>
       <c r="F32">
-        <v>-3.174626269694902</v>
+        <v>-2.706313728726618</v>
       </c>
       <c r="G32">
-        <v>-8.444500985694807</v>
+        <v>-9.660338561538621</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.242639379669655</v>
       </c>
       <c r="E33">
-        <v>-16.64189046035174</v>
+        <v>-18.50729570138337</v>
       </c>
       <c r="F33">
-        <v>-3.023556078078954</v>
+        <v>-2.343339700167931</v>
       </c>
       <c r="G33">
-        <v>-8.292712472719222</v>
+        <v>-9.760936108840454</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.827310446604709</v>
       </c>
       <c r="E34">
-        <v>-16.35117601448132</v>
+        <v>-17.94375428197284</v>
       </c>
       <c r="F34">
-        <v>-3.077576401517718</v>
+        <v>-2.299934904996043</v>
       </c>
       <c r="G34">
-        <v>-7.895062984724125</v>
+        <v>-8.86474494699543</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.348379733836276</v>
       </c>
       <c r="E35">
-        <v>-17.14314271978676</v>
+        <v>-17.2778331221969</v>
       </c>
       <c r="F35">
-        <v>-3.03207086661233</v>
+        <v>-2.543435159783763</v>
       </c>
       <c r="G35">
-        <v>-8.462149503964662</v>
+        <v>-9.539692350450961</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.79124936519481</v>
       </c>
       <c r="E36">
-        <v>-16.0281599635142</v>
+        <v>-16.58908392494829</v>
       </c>
       <c r="F36">
-        <v>-2.74521303359468</v>
+        <v>-2.72360921172967</v>
       </c>
       <c r="G36">
-        <v>-7.55490443056401</v>
+        <v>-8.967798919087404</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.141293223145284</v>
       </c>
       <c r="E37">
-        <v>-16.35155640629797</v>
+        <v>-17.03668282434044</v>
       </c>
       <c r="F37">
-        <v>-3.408722897726042</v>
+        <v>-2.49513802673094</v>
       </c>
       <c r="G37">
-        <v>-7.582888472007469</v>
+        <v>-8.821744270985837</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.387552491239753</v>
       </c>
       <c r="E38">
-        <v>-15.06554677217771</v>
+        <v>-16.59314143765916</v>
       </c>
       <c r="F38">
-        <v>-2.561126602405352</v>
+        <v>-2.152521127096051</v>
       </c>
       <c r="G38">
-        <v>-7.756298157900034</v>
+        <v>-8.761111629434085</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.523466267196085</v>
       </c>
       <c r="E39">
-        <v>-15.02404783637142</v>
+        <v>-16.34660225573358</v>
       </c>
       <c r="F39">
-        <v>-2.724943711615579</v>
+        <v>-2.565671854344513</v>
       </c>
       <c r="G39">
-        <v>-8.04043897099014</v>
+        <v>-8.477980532733456</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.550366847452117</v>
       </c>
       <c r="E40">
-        <v>-16.01391791276007</v>
+        <v>-16.27060087646284</v>
       </c>
       <c r="F40">
-        <v>-2.971538747020159</v>
+        <v>-2.643107639158211</v>
       </c>
       <c r="G40">
-        <v>-7.265721656617593</v>
+        <v>-8.195140764040284</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.475779999827992</v>
       </c>
       <c r="E41">
-        <v>-13.6466626537244</v>
+        <v>-15.37570648543707</v>
       </c>
       <c r="F41">
-        <v>-2.666401330524933</v>
+        <v>-2.633110901341226</v>
       </c>
       <c r="G41">
-        <v>-6.344125368304202</v>
+        <v>-8.0626990791962</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.312971550562773</v>
       </c>
       <c r="E42">
-        <v>-13.55460330562247</v>
+        <v>-14.87355305967452</v>
       </c>
       <c r="F42">
-        <v>-3.151615051612535</v>
+        <v>-2.564083045665944</v>
       </c>
       <c r="G42">
-        <v>-6.9590823760426</v>
+        <v>-8.552802172466524</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.080871002748032</v>
       </c>
       <c r="E43">
-        <v>-13.3505276244668</v>
+        <v>-14.44121511768822</v>
       </c>
       <c r="F43">
-        <v>-2.842009421346608</v>
+        <v>-2.453983077425056</v>
       </c>
       <c r="G43">
-        <v>-6.197021277266686</v>
+        <v>-8.372738290040026</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.806915000853937</v>
       </c>
       <c r="E44">
-        <v>-12.37518036422076</v>
+        <v>-13.76808009881806</v>
       </c>
       <c r="F44">
-        <v>-3.059127002722567</v>
+        <v>-2.521938197313713</v>
       </c>
       <c r="G44">
-        <v>-5.969914542727144</v>
+        <v>-8.070326576118681</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.523540834474442</v>
       </c>
       <c r="E45">
-        <v>-12.09580974573956</v>
+        <v>-13.70219080200645</v>
       </c>
       <c r="F45">
-        <v>-3.900798814378436</v>
+        <v>-2.784557171758046</v>
       </c>
       <c r="G45">
-        <v>-7.139848094123424</v>
+        <v>-7.696049539630837</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.26354346845334</v>
       </c>
       <c r="E46">
-        <v>-11.82583118235027</v>
+        <v>-13.49892118922416</v>
       </c>
       <c r="F46">
-        <v>-3.326248154001116</v>
+        <v>-2.670627661014016</v>
       </c>
       <c r="G46">
-        <v>-6.000917801702419</v>
+        <v>-7.856488508100536</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.057507126661029</v>
       </c>
       <c r="E47">
-        <v>-11.71237026608808</v>
+        <v>-13.2967972803658</v>
       </c>
       <c r="F47">
-        <v>-3.463337988960017</v>
+        <v>-3.06068433343983</v>
       </c>
       <c r="G47">
-        <v>-6.718766564801365</v>
+        <v>-8.148829542491418</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.934626898856664</v>
       </c>
       <c r="E48">
-        <v>-10.47017361799204</v>
+        <v>-11.53900216717843</v>
       </c>
       <c r="F48">
-        <v>-3.623825889578393</v>
+        <v>-3.093716311993863</v>
       </c>
       <c r="G48">
-        <v>-6.768878292629313</v>
+        <v>-8.073978107848497</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.919150940879883</v>
       </c>
       <c r="E49">
-        <v>-9.37835853474272</v>
+        <v>-11.97212806364206</v>
       </c>
       <c r="F49">
-        <v>-3.782222990872103</v>
+        <v>-3.091154171617005</v>
       </c>
       <c r="G49">
-        <v>-5.764167448006979</v>
+        <v>-7.787725166704335</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.024640036803607</v>
       </c>
       <c r="E50">
-        <v>-10.1371134116759</v>
+        <v>-11.16427094304371</v>
       </c>
       <c r="F50">
-        <v>-3.858214102935319</v>
+        <v>-3.075722515270253</v>
       </c>
       <c r="G50">
-        <v>-6.585795192670998</v>
+        <v>-7.326619141812487</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.253483785002326</v>
       </c>
       <c r="E51">
-        <v>-10.61786526927821</v>
+        <v>-10.86037410933697</v>
       </c>
       <c r="F51">
-        <v>-4.051970895184929</v>
+        <v>-3.614674086512264</v>
       </c>
       <c r="G51">
-        <v>-6.169057099096463</v>
+        <v>-7.986937244529979</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.600512090844594</v>
       </c>
       <c r="E52">
-        <v>-9.764166406300204</v>
+        <v>-10.33445072350816</v>
       </c>
       <c r="F52">
-        <v>-4.238404091226388</v>
+        <v>-3.359423440115833</v>
       </c>
       <c r="G52">
-        <v>-5.484889826314062</v>
+        <v>-8.009107968006479</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.055801426602239</v>
       </c>
       <c r="E53">
-        <v>-9.758551098530694</v>
+        <v>-9.682382165721677</v>
       </c>
       <c r="F53">
-        <v>-3.954781032916671</v>
+        <v>-3.223595208711395</v>
       </c>
       <c r="G53">
-        <v>-6.031901197404458</v>
+        <v>-7.781339124359081</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.599867835624865</v>
       </c>
       <c r="E54">
-        <v>-9.276458812622122</v>
+        <v>-10.54597574440644</v>
       </c>
       <c r="F54">
-        <v>-4.213139713808406</v>
+        <v>-3.308160751760988</v>
       </c>
       <c r="G54">
-        <v>-6.033814692726157</v>
+        <v>-8.239760296818581</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.207294429646202</v>
       </c>
       <c r="E55">
-        <v>-7.895840299533622</v>
+        <v>-9.551468510633935</v>
       </c>
       <c r="F55">
-        <v>-4.25464340579087</v>
+        <v>-3.530530182470696</v>
       </c>
       <c r="G55">
-        <v>-6.42730613552393</v>
+        <v>-8.023131438910831</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.84889806787929</v>
       </c>
       <c r="E56">
-        <v>-8.817796851229238</v>
+        <v>-9.668973354184965</v>
       </c>
       <c r="F56">
-        <v>-4.311802413318842</v>
+        <v>-3.886551723417687</v>
       </c>
       <c r="G56">
-        <v>-6.242369130063623</v>
+        <v>-8.102505078760396</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.492688345362673</v>
       </c>
       <c r="E57">
-        <v>-7.097628828571606</v>
+        <v>-8.551672019220474</v>
       </c>
       <c r="F57">
-        <v>-4.195607317728155</v>
+        <v>-3.715799522311222</v>
       </c>
       <c r="G57">
-        <v>-6.564577906309809</v>
+        <v>-7.693619599205013</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.097668551598073</v>
       </c>
       <c r="E58">
-        <v>-7.714828136499023</v>
+        <v>-8.986319482950682</v>
       </c>
       <c r="F58">
-        <v>-4.23394250439491</v>
+        <v>-3.905389626524751</v>
       </c>
       <c r="G58">
-        <v>-6.705703152103401</v>
+        <v>-7.928496184125224</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.619843792582563</v>
       </c>
       <c r="E59">
-        <v>-5.704525312643959</v>
+        <v>-7.764301715032821</v>
       </c>
       <c r="F59">
-        <v>-4.220628983497116</v>
+        <v>-3.707052790905062</v>
       </c>
       <c r="G59">
-        <v>-6.089097492686446</v>
+        <v>-7.362018805263914</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.02100982014952</v>
       </c>
       <c r="E60">
-        <v>-5.780576505128775</v>
+        <v>-7.956476566496328</v>
       </c>
       <c r="F60">
-        <v>-4.753518562085441</v>
+        <v>-3.888521581101544</v>
       </c>
       <c r="G60">
-        <v>-6.584828513373531</v>
+        <v>-7.731220775440055</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-10.27643923213598</v>
       </c>
       <c r="E61">
-        <v>-5.35989938371223</v>
+        <v>-7.859227587181607</v>
       </c>
       <c r="F61">
-        <v>-4.466758476421322</v>
+        <v>-3.996920911064485</v>
       </c>
       <c r="G61">
-        <v>-6.687150854901326</v>
+        <v>-8.09109031774099</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-10.37247978806187</v>
       </c>
       <c r="E62">
-        <v>-4.735033369289828</v>
+        <v>-7.307840592007664</v>
       </c>
       <c r="F62">
-        <v>-4.532163881444163</v>
+        <v>-4.129260058968331</v>
       </c>
       <c r="G62">
-        <v>-6.595733450379891</v>
+        <v>-7.713370313892304</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-10.30630630173521</v>
       </c>
       <c r="E63">
-        <v>-6.624679531684522</v>
+        <v>-7.752935245273568</v>
       </c>
       <c r="F63">
-        <v>-4.570646517508616</v>
+        <v>-3.854003511426889</v>
       </c>
       <c r="G63">
-        <v>-7.246881341953602</v>
+        <v>-8.427160348160104</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-10.0860625007719</v>
       </c>
       <c r="E64">
-        <v>-5.429058238757371</v>
+        <v>-6.520239335645621</v>
       </c>
       <c r="F64">
-        <v>-4.677766848201634</v>
+        <v>-4.222092708697863</v>
       </c>
       <c r="G64">
-        <v>-7.515869788110463</v>
+        <v>-7.448735235119583</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.731568119263418</v>
       </c>
       <c r="E65">
-        <v>-5.353867456334013</v>
+        <v>-7.058756407689764</v>
       </c>
       <c r="F65">
-        <v>-4.583217821213502</v>
+        <v>-4.10647250008472</v>
       </c>
       <c r="G65">
-        <v>-7.197719740695424</v>
+        <v>-8.410339466275067</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.269697717006638</v>
       </c>
       <c r="E66">
-        <v>-5.82690732270125</v>
+        <v>-7.16756205267206</v>
       </c>
       <c r="F66">
-        <v>-4.682761903640515</v>
+        <v>-3.911855862471004</v>
       </c>
       <c r="G66">
-        <v>-7.376528926362539</v>
+        <v>-8.277440926146564</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.730657301486854</v>
       </c>
       <c r="E67">
-        <v>-3.353264623803379</v>
+        <v>-7.233229454257287</v>
       </c>
       <c r="F67">
-        <v>-4.694093969710813</v>
+        <v>-4.106743376225435</v>
       </c>
       <c r="G67">
-        <v>-7.454532000358848</v>
+        <v>-8.273210048947377</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.145103065135981</v>
       </c>
       <c r="E68">
-        <v>-5.459000508896088</v>
+        <v>-7.281362604484816</v>
       </c>
       <c r="F68">
-        <v>-4.803392906673194</v>
+        <v>-3.978560147581434</v>
       </c>
       <c r="G68">
-        <v>-6.568563803139092</v>
+        <v>-7.930406368901384</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.546326188746617</v>
       </c>
       <c r="E69">
-        <v>-4.411138794365213</v>
+        <v>-5.824733655177568</v>
       </c>
       <c r="F69">
-        <v>-5.097922250208169</v>
+        <v>-4.231455745451706</v>
       </c>
       <c r="G69">
-        <v>-6.411210263111993</v>
+        <v>-7.88390644625678</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.964469805652225</v>
       </c>
       <c r="E70">
-        <v>-5.326904922092343</v>
+        <v>-6.44845396567603</v>
       </c>
       <c r="F70">
-        <v>-5.027263339116774</v>
+        <v>-4.206227816199447</v>
       </c>
       <c r="G70">
-        <v>-6.346846636737483</v>
+        <v>-8.137080416372545</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.422791203851213</v>
       </c>
       <c r="E71">
-        <v>-5.377170983577484</v>
+        <v>-6.705327125287123</v>
       </c>
       <c r="F71">
-        <v>-5.290626187488821</v>
+        <v>-4.613329804672667</v>
       </c>
       <c r="G71">
-        <v>-6.984533850148517</v>
+        <v>-7.326930333093179</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.933877707069652</v>
       </c>
       <c r="E72">
-        <v>-4.579688596930703</v>
+        <v>-6.248721091093721</v>
       </c>
       <c r="F72">
-        <v>-5.224213487704176</v>
+        <v>-4.337725342822049</v>
       </c>
       <c r="G72">
-        <v>-6.412653660967115</v>
+        <v>-7.765097587943417</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.506397874758287</v>
       </c>
       <c r="E73">
-        <v>-4.958214682283853</v>
+        <v>-7.190593871475071</v>
       </c>
       <c r="F73">
-        <v>-5.321060405867675</v>
+        <v>-4.178500702492942</v>
       </c>
       <c r="G73">
-        <v>-6.407015801913737</v>
+        <v>-7.764276572649678</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.141894197566817</v>
       </c>
       <c r="E74">
-        <v>-5.667971470454043</v>
+        <v>-7.068488098332248</v>
       </c>
       <c r="F74">
-        <v>-5.208481133990208</v>
+        <v>-4.168113803629239</v>
       </c>
       <c r="G74">
-        <v>-5.719501567591132</v>
+        <v>-7.208770341705511</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.836333428915534</v>
       </c>
       <c r="E75">
-        <v>-4.654838623087993</v>
+        <v>-7.098235644088634</v>
       </c>
       <c r="F75">
-        <v>-5.610815039692914</v>
+        <v>-4.690268569044685</v>
       </c>
       <c r="G75">
-        <v>-5.837724459344045</v>
+        <v>-7.297181770877287</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.581386122814271</v>
       </c>
       <c r="E76">
-        <v>-5.726212174666692</v>
+        <v>-7.635919476915366</v>
       </c>
       <c r="F76">
-        <v>-5.884168827310125</v>
+        <v>-4.547757897801864</v>
       </c>
       <c r="G76">
-        <v>-5.996931904873136</v>
+        <v>-6.743526134889574</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.372203279338103</v>
       </c>
       <c r="E77">
-        <v>-7.07938813526871</v>
+        <v>-8.141134151107103</v>
       </c>
       <c r="F77">
-        <v>-5.071292723310373</v>
+        <v>-4.570287834423205</v>
       </c>
       <c r="G77">
-        <v>-6.250509761544691</v>
+        <v>-6.918889042650308</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.203917183191767</v>
       </c>
       <c r="E78">
-        <v>-6.384321716779402</v>
+        <v>-7.891701274290611</v>
       </c>
       <c r="F78">
-        <v>-5.633966251866354</v>
+        <v>-4.862243440437682</v>
       </c>
       <c r="G78">
-        <v>-5.828683359476296</v>
+        <v>-7.01822527210168</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.070930658726176</v>
       </c>
       <c r="E79">
-        <v>-7.34400498543292</v>
+        <v>-8.895297155396507</v>
       </c>
       <c r="F79">
-        <v>-5.778436012016797</v>
+        <v>-5.242824418142873</v>
       </c>
       <c r="G79">
-        <v>-5.852333896808849</v>
+        <v>-6.581643768564753</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.966516262071731</v>
       </c>
       <c r="E80">
-        <v>-8.942565367088571</v>
+        <v>-9.236816551158975</v>
       </c>
       <c r="F80">
-        <v>-5.569386729144105</v>
+        <v>-5.105383355405184</v>
       </c>
       <c r="G80">
-        <v>-4.73458778529364</v>
+        <v>-6.261576915282475</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.885654853613979</v>
       </c>
       <c r="E81">
-        <v>-8.718310805754728</v>
+        <v>-10.37502585061688</v>
       </c>
       <c r="F81">
-        <v>-5.7092855579659</v>
+        <v>-5.124176526672497</v>
       </c>
       <c r="G81">
-        <v>-5.005870439509217</v>
+        <v>-6.279619388471503</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.823834263738103</v>
       </c>
       <c r="E82">
-        <v>-9.969007399563166</v>
+        <v>-11.38205431502059</v>
       </c>
       <c r="F82">
-        <v>-5.836456521643679</v>
+        <v>-4.886496381256846</v>
       </c>
       <c r="G82">
-        <v>-4.812107519641214</v>
+        <v>-6.080718501926551</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.773740689413024</v>
       </c>
       <c r="E83">
-        <v>-11.75711158928387</v>
+        <v>-11.65743534790104</v>
       </c>
       <c r="F83">
-        <v>-6.065582945258023</v>
+        <v>-5.294228757323596</v>
       </c>
       <c r="G83">
-        <v>-5.063566627167636</v>
+        <v>-6.282920002374156</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.725107820197395</v>
       </c>
       <c r="E84">
-        <v>-10.76730491153133</v>
+        <v>-12.35289574362901</v>
       </c>
       <c r="F84">
-        <v>-6.409614696416894</v>
+        <v>-5.460821725700605</v>
       </c>
       <c r="G84">
-        <v>-5.093825013396574</v>
+        <v>-5.849996651658124</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.667319711123262</v>
       </c>
       <c r="E85">
-        <v>-12.49411620555821</v>
+        <v>-12.77054784440843</v>
       </c>
       <c r="F85">
-        <v>-6.233356337184021</v>
+        <v>-5.824344961847348</v>
       </c>
       <c r="G85">
-        <v>-5.256290035736308</v>
+        <v>-5.903326229750244</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.592867626309347</v>
       </c>
       <c r="E86">
-        <v>-13.61662528563152</v>
+        <v>-14.57879921498926</v>
       </c>
       <c r="F86">
-        <v>-6.72640765645321</v>
+        <v>-5.762957138728085</v>
       </c>
       <c r="G86">
-        <v>-5.590079100278865</v>
+        <v>-4.892043952232456</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.497891037587638</v>
       </c>
       <c r="E87">
-        <v>-15.03400595071429</v>
+        <v>-15.76704362375792</v>
       </c>
       <c r="F87">
-        <v>-6.297078085460671</v>
+        <v>-5.828640046830864</v>
       </c>
       <c r="G87">
-        <v>-5.575830512277841</v>
+        <v>-5.878944061853511</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.3819062832044</v>
       </c>
       <c r="E88">
-        <v>-15.70528882371531</v>
+        <v>-16.19959440402257</v>
       </c>
       <c r="F88">
-        <v>-6.702254533906084</v>
+        <v>-5.733537670417661</v>
       </c>
       <c r="G88">
-        <v>-5.000805304834133</v>
+        <v>-5.166951653813536</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.247407862941161</v>
       </c>
       <c r="E89">
-        <v>-17.31806861375505</v>
+        <v>-18.05808466524449</v>
       </c>
       <c r="F89">
-        <v>-6.848350793451923</v>
+        <v>-6.10419977684173</v>
       </c>
       <c r="G89">
-        <v>-4.873326127753417</v>
+        <v>-5.659931611157487</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.101884033428056</v>
       </c>
       <c r="E90">
-        <v>-19.74222867717111</v>
+        <v>-20.23824602065326</v>
       </c>
       <c r="F90">
-        <v>-6.442852938454224</v>
+        <v>-6.158836405628177</v>
       </c>
       <c r="G90">
-        <v>-5.024002297427805</v>
+        <v>-5.444709735103928</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.956520924997214</v>
       </c>
       <c r="E91">
-        <v>-21.36243516458342</v>
+        <v>-21.5120242464788</v>
       </c>
       <c r="F91">
-        <v>-7.12847938387293</v>
+        <v>-6.200725288452943</v>
       </c>
       <c r="G91">
-        <v>-4.041995174113794</v>
+        <v>-6.106868501141254</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.824981326394231</v>
       </c>
       <c r="E92">
-        <v>-23.63879036486313</v>
+        <v>-23.67794355113345</v>
       </c>
       <c r="F92">
-        <v>-6.949271208318688</v>
+        <v>-6.425306460128125</v>
       </c>
       <c r="G92">
-        <v>-5.752669923349091</v>
+        <v>-5.994760186999375</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.722413594520149</v>
       </c>
       <c r="E93">
-        <v>-25.83041328798531</v>
+        <v>-25.47925729953452</v>
       </c>
       <c r="F93">
-        <v>-6.844101682859263</v>
+        <v>-6.500759547563222</v>
       </c>
       <c r="G93">
-        <v>-5.842107621638041</v>
+        <v>-6.182113890703349</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.66601840293585</v>
       </c>
       <c r="E94">
-        <v>-28.19448502979359</v>
+        <v>-27.40779399670709</v>
       </c>
       <c r="F94">
-        <v>-7.684516032797681</v>
+        <v>-6.203939353975804</v>
       </c>
       <c r="G94">
-        <v>-5.42057916866818</v>
+        <v>-6.432520244748282</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-2.671068807990275</v>
       </c>
       <c r="E95">
-        <v>-29.38955837736582</v>
+        <v>-29.87783655876886</v>
       </c>
       <c r="F95">
-        <v>-6.714349940538061</v>
+        <v>-6.052250371909965</v>
       </c>
       <c r="G95">
-        <v>-6.778207409958979</v>
+        <v>-6.825938855544191</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.748856609148515</v>
       </c>
       <c r="E96">
-        <v>-31.99424379286065</v>
+        <v>-31.47162392882043</v>
       </c>
       <c r="F96">
-        <v>-6.80658989339089</v>
+        <v>-6.420431103778949</v>
       </c>
       <c r="G96">
-        <v>-6.626753262082862</v>
+        <v>-7.410495123595462</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.895381348532089</v>
       </c>
       <c r="E97">
-        <v>-34.44657322884142</v>
+        <v>-34.80620199216056</v>
       </c>
       <c r="F97">
-        <v>-7.20004535727039</v>
+        <v>-6.585203734788305</v>
       </c>
       <c r="G97">
-        <v>-7.07622934049525</v>
+        <v>-7.349693644221207</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.110394093959314</v>
       </c>
       <c r="E98">
-        <v>-36.54534205667333</v>
+        <v>-37.3640765718381</v>
       </c>
       <c r="F98">
-        <v>-6.850316095115065</v>
+        <v>-6.362260245468457</v>
       </c>
       <c r="G98">
-        <v>-7.493351457352341</v>
+        <v>-8.514869941677555</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.369499340854892</v>
       </c>
       <c r="E99">
-        <v>-40.28128556402429</v>
+        <v>-39.11109165265021</v>
       </c>
       <c r="F99">
-        <v>-7.627608020592758</v>
+        <v>-6.504439569750159</v>
       </c>
       <c r="G99">
-        <v>-7.953182922211569</v>
+        <v>-8.716786735208784</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.671107291027684</v>
       </c>
       <c r="E100">
-        <v>-42.30650065278661</v>
+        <v>-41.52290030321034</v>
       </c>
       <c r="F100">
-        <v>-6.806307834290236</v>
+        <v>-6.447182400684956</v>
       </c>
       <c r="G100">
-        <v>-8.393773496396554</v>
+        <v>-9.158519447604816</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.966838758814163</v>
       </c>
       <c r="E101">
-        <v>-44.77645038113123</v>
+        <v>-43.84593274932411</v>
       </c>
       <c r="F101">
-        <v>-7.272171721215845</v>
+        <v>-6.335184642724254</v>
       </c>
       <c r="G101">
-        <v>-7.978650949045183</v>
+        <v>-8.819542758202221</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.286799576874883</v>
       </c>
       <c r="E102">
-        <v>-46.50085931969704</v>
+        <v>-46.26864143682071</v>
       </c>
       <c r="F102">
-        <v>-7.057506107352173</v>
+        <v>-6.207123598272166</v>
       </c>
       <c r="G102">
-        <v>-9.092738907739498</v>
+        <v>-10.00738636096596</v>
       </c>
     </row>
   </sheetData>
